--- a/layout/Layout_REPORTOS_MN_ME_V7.1_2024_CANASTA_REPORTOS.xlsx
+++ b/layout/Layout_REPORTOS_MN_ME_V7.1_2024_CANASTA_REPORTOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B3008F-775D-48D2-93DE-C7EC0A7EEBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875C7A8A-E5FE-4AD1-AA4E-D76911CCDEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="610" yWindow="1690" windowWidth="26520" windowHeight="15950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CANASTA_REPORTOS" sheetId="4" r:id="rId1"/>
@@ -245,9 +245,6 @@
     <t>SECCION</t>
   </si>
   <si>
-    <t>Seccion</t>
-  </si>
-  <si>
     <t>12 </t>
   </si>
   <si>
@@ -255,13 +252,16 @@
   </si>
   <si>
     <t>Cruce con Vector</t>
+  </si>
+  <si>
+    <t>SECCION_CANASTA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1081,18 +1081,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8ECF5F-2CA7-4840-81E2-F154F848061C}">
   <dimension ref="A1:U15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="28.453125" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.81640625" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.85546875" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="T1" s="1"/>
       <c r="U1"/>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A3" s="5" t="s">
         <v>46</v>
       </c>
@@ -1226,7 +1226,7 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A4" s="5" t="s">
         <v>46</v>
       </c>
@@ -1266,7 +1266,7 @@
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A5" s="5" t="s">
         <v>46</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -1346,7 +1346,7 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A9" s="5" t="s">
         <v>46</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
@@ -1530,16 +1530,16 @@
         <v>23</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="K11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -1550,7 +1550,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A12" s="5" t="s">
         <v>46</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="6"/>
       <c r="J12" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="6" t="s">
@@ -1588,7 +1588,7 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:21" s="4" customFormat="1" ht="18">
       <c r="A13" s="5" t="s">
         <v>46</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="H13" s="5"/>
       <c r="I13" s="6"/>
       <c r="J13" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="6" t="s">
@@ -1626,7 +1626,7 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" ht="18" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:21" ht="18">
       <c r="A14" s="5" t="s">
         <v>46</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="6"/>
       <c r="J14" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="6" t="s">
@@ -1660,7 +1660,7 @@
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
     </row>
-    <row r="15" spans="1:21" ht="18" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:21" ht="18">
       <c r="A15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1705,12 +1705,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1915,20 +1917,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0FB066D-DC24-490D-9537-E3210F529E79}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E5E09E5-67A3-4C90-83A7-4274DDC3623C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
+    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1953,12 +1956,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E5E09E5-67A3-4C90-83A7-4274DDC3623C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0FB066D-DC24-490D-9537-E3210F529E79}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
-    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>